--- a/quizzes/sculpture-16e-niveau1.xlsx
+++ b/quizzes/sculpture-16e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7C5D9CEF-86D9-48A7-8434-BC6204BF1A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2CEC34-C5C6-40F6-BBFE-D30F79C35827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E4C78D6-3AB9-4FEC-9C8D-3201C3789B3A}"/>
   </bookViews>
@@ -161,9 +161,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c9/Pierino_da_vinci%2C_sansone_e_il_filisteo%2C_02.jpg/960px-Pierino_da_vinci%2C_sansone_e_il_filisteo%2C_02.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>La Châsse de saint Sebald (Sebaldusgrab)</t>
-  </si>
-  <si>
     <t>Église Saint-Sebald, Nuremberg</t>
   </si>
   <si>
@@ -486,6 +483,9 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t>La Châsse de Saint Sebald (Sebaldusgrab)</t>
   </si>
 </sst>
 </file>
@@ -964,398 +964,400 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="87.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
     <col min="5" max="5" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="45.75" thickBot="1">
       <c r="A1" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:5">

--- a/quizzes/sculpture-16e-niveau1.xlsx
+++ b/quizzes/sculpture-16e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2CEC34-C5C6-40F6-BBFE-D30F79C35827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D702DE-F1D1-41A3-96AE-2D1628255FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E4C78D6-3AB9-4FEC-9C8D-3201C3789B3A}"/>
   </bookViews>
@@ -101,21 +101,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Tilman_Riemenschneider_Heilig_Blut_Altar_1.jpg/1280px-Tilman_Riemenschneider_Heilig_Blut_Altar_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Sainte Cécile</t>
-  </si>
-  <si>
-    <t>Santa Cecilia in Trastevere, Rome</t>
-  </si>
-  <si>
-    <t>1600</t>
-  </si>
-  <si>
-    <t>Stefano MADERNO</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e6/Stefano_Maderno_-_Martyrdom_of_Saint_Cecilia_-_Church_of_St._Cecilia_-_Rome.jpg/1280px-Stefano_Maderno_-_Martyrdom_of_Saint_Cecilia_-_Church_of_St._Cecilia_-_Rome.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Cénotaphes de Charles Quint et de Philippe II et leurs familles</t>
   </si>
   <si>
@@ -486,6 +471,21 @@
   </si>
   <si>
     <t>La Châsse de Saint Sebald (Sebaldusgrab)</t>
+  </si>
+  <si>
+    <t>Cornelis FLORIS</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b8/Eglise_Saint-L%C3%A9onard_de_L%C3%A9au_06.JPG/960px-Eglise_Saint-L%C3%A9onard_de_L%C3%A9au_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Eglise Saint-Léonard, Léau</t>
+  </si>
+  <si>
+    <t>Tabernacle</t>
+  </si>
+  <si>
+    <t>1550-1552</t>
   </si>
 </sst>
 </file>
@@ -971,172 +971,172 @@
   <sheetData>
     <row r="1" spans="1:5" ht="45.75" thickBot="1">
       <c r="A1" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
-        <v>106</v>
+      <c r="A10" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>102</v>
+        <v>144</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1150,24 +1150,24 @@
         <v>99</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>93</v>
@@ -1218,24 +1218,24 @@
         <v>80</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>74</v>
@@ -1344,41 +1344,41 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>148</v>
+      <c r="E23" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>39</v>
+      <c r="A24" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E24" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -1497,37 +1497,40 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
+    <sortCondition ref="B2:B31"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{5242106A-D01E-4A04-8EFB-AF043EE2BA4E}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{FCA79AE7-C90D-4ADA-B4A8-99FD2628142E}"/>
     <hyperlink ref="A6" r:id="rId3" xr:uid="{181DE111-7A4C-4E33-A359-2717C94FE5EA}"/>
     <hyperlink ref="A8" r:id="rId4" xr:uid="{097E2776-6480-4CE6-AB9D-AA7955DE5BBD}"/>
     <hyperlink ref="A9" r:id="rId5" xr:uid="{930DCDD0-A1B8-49B0-BB94-A6B5552DD1CD}"/>
-    <hyperlink ref="A11" r:id="rId6" xr:uid="{758FFE4E-10F1-4886-9056-B6BC5616958F}"/>
-    <hyperlink ref="A12" r:id="rId7" xr:uid="{7A4E7F06-7D04-4BA0-9744-1490B8A35F33}"/>
-    <hyperlink ref="A13" r:id="rId8" xr:uid="{4AA7D489-7BA4-4586-A19F-377B137120B7}"/>
-    <hyperlink ref="A15" r:id="rId9" xr:uid="{93B309C4-F315-4C59-B502-D4414F3A4480}"/>
-    <hyperlink ref="A16" r:id="rId10" xr:uid="{16B09C70-948A-4AE4-BABE-ECEAC1F85703}"/>
-    <hyperlink ref="A17" r:id="rId11" xr:uid="{5B64713D-E5CC-4F23-B634-89A631965B24}"/>
-    <hyperlink ref="A18" r:id="rId12" xr:uid="{2BF29914-DDB3-4B41-979B-0508649D021D}"/>
-    <hyperlink ref="A19" r:id="rId13" xr:uid="{4C4ADE0F-0368-4969-8524-83327C5DF3A0}"/>
-    <hyperlink ref="A20" r:id="rId14" xr:uid="{07885347-8B52-42A6-96F4-41EA9F98E84F}"/>
-    <hyperlink ref="A25" r:id="rId15" xr:uid="{2A013176-5A8A-4111-8236-D04C279E786C}"/>
-    <hyperlink ref="A26" r:id="rId16" xr:uid="{5354361B-D69D-44F2-A18C-F6113D885E56}"/>
-    <hyperlink ref="A21" r:id="rId17" xr:uid="{D4E90678-E0A3-41F2-AEA7-D60E006449EF}"/>
+    <hyperlink ref="A12" r:id="rId6" xr:uid="{758FFE4E-10F1-4886-9056-B6BC5616958F}"/>
+    <hyperlink ref="A13" r:id="rId7" xr:uid="{7A4E7F06-7D04-4BA0-9744-1490B8A35F33}"/>
+    <hyperlink ref="A14" r:id="rId8" xr:uid="{4AA7D489-7BA4-4586-A19F-377B137120B7}"/>
+    <hyperlink ref="A16" r:id="rId9" xr:uid="{93B309C4-F315-4C59-B502-D4414F3A4480}"/>
+    <hyperlink ref="A17" r:id="rId10" xr:uid="{16B09C70-948A-4AE4-BABE-ECEAC1F85703}"/>
+    <hyperlink ref="A18" r:id="rId11" xr:uid="{5B64713D-E5CC-4F23-B634-89A631965B24}"/>
+    <hyperlink ref="A19" r:id="rId12" xr:uid="{2BF29914-DDB3-4B41-979B-0508649D021D}"/>
+    <hyperlink ref="A20" r:id="rId13" xr:uid="{4C4ADE0F-0368-4969-8524-83327C5DF3A0}"/>
+    <hyperlink ref="A21" r:id="rId14" xr:uid="{07885347-8B52-42A6-96F4-41EA9F98E84F}"/>
+    <hyperlink ref="A26" r:id="rId15" xr:uid="{2A013176-5A8A-4111-8236-D04C279E786C}"/>
+    <hyperlink ref="A27" r:id="rId16" xr:uid="{5354361B-D69D-44F2-A18C-F6113D885E56}"/>
+    <hyperlink ref="A22" r:id="rId17" xr:uid="{D4E90678-E0A3-41F2-AEA7-D60E006449EF}"/>
     <hyperlink ref="A31" r:id="rId18" xr:uid="{16B2D77D-2135-4F0D-8D53-A579C53D4507}"/>
     <hyperlink ref="A5" r:id="rId19" xr:uid="{5DBEDAD7-DD60-4052-8E67-A166D5D6995E}"/>
     <hyperlink ref="A29" r:id="rId20" xr:uid="{DD0F6C84-E514-47F0-8E72-EE3C1E37E23D}"/>
-    <hyperlink ref="A27" r:id="rId21" xr:uid="{24E0BDCF-1CF3-40F3-AE68-A4428FBC9177}"/>
-    <hyperlink ref="A10" r:id="rId22" xr:uid="{BD0C5373-3553-4D1A-A8C8-CFAA52307DCE}"/>
-    <hyperlink ref="A22" r:id="rId23" xr:uid="{697C69DD-982A-45AE-8361-B540DB2E7029}"/>
-    <hyperlink ref="A30" r:id="rId24" xr:uid="{CBBCB0C1-5DDE-4827-9759-9867A464E0B2}"/>
-    <hyperlink ref="A28" r:id="rId25" xr:uid="{145092A2-42AD-48EB-BC53-D1FDC7661D74}"/>
-    <hyperlink ref="A14" r:id="rId26" xr:uid="{34A209BD-B631-43C3-8D8F-0D37F800AD46}"/>
-    <hyperlink ref="A24" r:id="rId27" xr:uid="{C02A9167-4008-4FA8-A6D6-B649BB1C4F11}"/>
-    <hyperlink ref="A3" r:id="rId28" xr:uid="{F107AA1F-8401-4D3B-A335-E67CB6C2123D}"/>
-    <hyperlink ref="A23" r:id="rId29" xr:uid="{2B0D4300-DCC4-4D06-B4A9-8FED1BE0DE59}"/>
-    <hyperlink ref="A7" r:id="rId30" xr:uid="{6AC9E8EE-7C2D-4468-ABD9-C8B58F14FE48}"/>
+    <hyperlink ref="A11" r:id="rId21" xr:uid="{BD0C5373-3553-4D1A-A8C8-CFAA52307DCE}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{697C69DD-982A-45AE-8361-B540DB2E7029}"/>
+    <hyperlink ref="A30" r:id="rId23" xr:uid="{CBBCB0C1-5DDE-4827-9759-9867A464E0B2}"/>
+    <hyperlink ref="A28" r:id="rId24" xr:uid="{145092A2-42AD-48EB-BC53-D1FDC7661D74}"/>
+    <hyperlink ref="A15" r:id="rId25" xr:uid="{34A209BD-B631-43C3-8D8F-0D37F800AD46}"/>
+    <hyperlink ref="A25" r:id="rId26" xr:uid="{C02A9167-4008-4FA8-A6D6-B649BB1C4F11}"/>
+    <hyperlink ref="A3" r:id="rId27" xr:uid="{F107AA1F-8401-4D3B-A335-E67CB6C2123D}"/>
+    <hyperlink ref="A24" r:id="rId28" xr:uid="{2B0D4300-DCC4-4D06-B4A9-8FED1BE0DE59}"/>
+    <hyperlink ref="A7" r:id="rId29" xr:uid="{6AC9E8EE-7C2D-4468-ABD9-C8B58F14FE48}"/>
+    <hyperlink ref="A10" r:id="rId30" xr:uid="{02B23578-D156-41EA-B9E2-8004FFFC437F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e-niveau1.xlsx
+++ b/quizzes/sculpture-16e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D702DE-F1D1-41A3-96AE-2D1628255FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5506CB1E-91F2-4AB0-901E-CD312BBB69DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E4C78D6-3AB9-4FEC-9C8D-3201C3789B3A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="147">
   <si>
     <t>L'Honneur triomphant du Mensonge</t>
   </si>
@@ -56,21 +56,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/L%27Onore_vince_l%27Inganno_by_Vincenzo_Danti-Museo_del_Bargello.jpg/1280px-L%27Onore_vince_l%27Inganno_by_Vincenzo_Danti-Museo_del_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Retable de l'église Notre-Dame (Marienaltar)</t>
-  </si>
-  <si>
-    <t>Basilique Notre-Dame, Cracovie</t>
-  </si>
-  <si>
-    <t>1477-1489</t>
-  </si>
-  <si>
-    <t>Veit STOSS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d0/Hochaltar_von_Veit_Sto%C3%9F%2C_Marienkirche%2C_Krakau%2C_Polen.JPG/1280px-Hochaltar_von_Veit_Sto%C3%9F%2C_Marienkirche%2C_Krakau%2C_Polen.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Atlas soutenant le monde</t>
   </si>
   <si>
@@ -486,6 +471,15 @@
   </si>
   <si>
     <t>1550-1552</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/02/La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg/960px-La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Michel COLOMBE</t>
+  </si>
+  <si>
+    <t>Vierge à l'enfant</t>
   </si>
 </sst>
 </file>
@@ -606,7 +600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -624,6 +618,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -969,514 +966,514 @@
     <col min="5" max="5" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="45.75" thickBot="1">
+    <row r="1" spans="1:5" ht="30.75" thickBot="1">
       <c r="A1" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>9</v>
+      <c r="A30" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>7</v>
+        <v>145</v>
+      </c>
+      <c r="C30" s="12">
+        <v>1500</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>5</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1518,19 +1515,18 @@
     <hyperlink ref="A26" r:id="rId15" xr:uid="{2A013176-5A8A-4111-8236-D04C279E786C}"/>
     <hyperlink ref="A27" r:id="rId16" xr:uid="{5354361B-D69D-44F2-A18C-F6113D885E56}"/>
     <hyperlink ref="A22" r:id="rId17" xr:uid="{D4E90678-E0A3-41F2-AEA7-D60E006449EF}"/>
-    <hyperlink ref="A31" r:id="rId18" xr:uid="{16B2D77D-2135-4F0D-8D53-A579C53D4507}"/>
-    <hyperlink ref="A5" r:id="rId19" xr:uid="{5DBEDAD7-DD60-4052-8E67-A166D5D6995E}"/>
-    <hyperlink ref="A29" r:id="rId20" xr:uid="{DD0F6C84-E514-47F0-8E72-EE3C1E37E23D}"/>
-    <hyperlink ref="A11" r:id="rId21" xr:uid="{BD0C5373-3553-4D1A-A8C8-CFAA52307DCE}"/>
-    <hyperlink ref="A23" r:id="rId22" xr:uid="{697C69DD-982A-45AE-8361-B540DB2E7029}"/>
-    <hyperlink ref="A30" r:id="rId23" xr:uid="{CBBCB0C1-5DDE-4827-9759-9867A464E0B2}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{145092A2-42AD-48EB-BC53-D1FDC7661D74}"/>
-    <hyperlink ref="A15" r:id="rId25" xr:uid="{34A209BD-B631-43C3-8D8F-0D37F800AD46}"/>
-    <hyperlink ref="A25" r:id="rId26" xr:uid="{C02A9167-4008-4FA8-A6D6-B649BB1C4F11}"/>
-    <hyperlink ref="A3" r:id="rId27" xr:uid="{F107AA1F-8401-4D3B-A335-E67CB6C2123D}"/>
-    <hyperlink ref="A24" r:id="rId28" xr:uid="{2B0D4300-DCC4-4D06-B4A9-8FED1BE0DE59}"/>
-    <hyperlink ref="A7" r:id="rId29" xr:uid="{6AC9E8EE-7C2D-4468-ABD9-C8B58F14FE48}"/>
-    <hyperlink ref="A10" r:id="rId30" xr:uid="{02B23578-D156-41EA-B9E2-8004FFFC437F}"/>
+    <hyperlink ref="A5" r:id="rId18" xr:uid="{5DBEDAD7-DD60-4052-8E67-A166D5D6995E}"/>
+    <hyperlink ref="A29" r:id="rId19" xr:uid="{DD0F6C84-E514-47F0-8E72-EE3C1E37E23D}"/>
+    <hyperlink ref="A11" r:id="rId20" xr:uid="{BD0C5373-3553-4D1A-A8C8-CFAA52307DCE}"/>
+    <hyperlink ref="A23" r:id="rId21" xr:uid="{697C69DD-982A-45AE-8361-B540DB2E7029}"/>
+    <hyperlink ref="A28" r:id="rId22" xr:uid="{145092A2-42AD-48EB-BC53-D1FDC7661D74}"/>
+    <hyperlink ref="A15" r:id="rId23" xr:uid="{34A209BD-B631-43C3-8D8F-0D37F800AD46}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{C02A9167-4008-4FA8-A6D6-B649BB1C4F11}"/>
+    <hyperlink ref="A3" r:id="rId25" xr:uid="{F107AA1F-8401-4D3B-A335-E67CB6C2123D}"/>
+    <hyperlink ref="A24" r:id="rId26" xr:uid="{2B0D4300-DCC4-4D06-B4A9-8FED1BE0DE59}"/>
+    <hyperlink ref="A7" r:id="rId27" xr:uid="{6AC9E8EE-7C2D-4468-ABD9-C8B58F14FE48}"/>
+    <hyperlink ref="A10" r:id="rId28" xr:uid="{02B23578-D156-41EA-B9E2-8004FFFC437F}"/>
+    <hyperlink ref="A30" r:id="rId29" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/02/La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg/960px-La_Vierge_et_l%27Enfant_-_Michel_Colombe_-_Mus%C3%A9e_du_Louvre_Sculptures_RFML.SC.2022.39.1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27A5B3C7-CC0F-45DB-8F82-B1D6B3263FF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-16e-niveau1.xlsx
+++ b/quizzes/sculpture-16e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5506CB1E-91F2-4AB0-901E-CD312BBB69DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550382B7-1C84-46B1-8E86-98F326CF4C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E4C78D6-3AB9-4FEC-9C8D-3201C3789B3A}"/>
   </bookViews>
@@ -218,9 +218,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Kaiser_Karl_V._%28Leoni_1555%29.jpg/1280px-Kaiser_Karl_V._%28Leoni_1555%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>El Entierro de Cristo (Santo Entierro)</t>
-  </si>
-  <si>
     <t>Museo Nacional de Escultura, Valladolid</t>
   </si>
   <si>
@@ -480,6 +477,9 @@
   </si>
   <si>
     <t>Vierge à l'enfant</t>
+  </si>
+  <si>
+    <t>L'Enterrement du Christ</t>
   </si>
 </sst>
 </file>
@@ -968,308 +968,308 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30.75" thickBot="1">
       <c r="A1" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1371,7 +1371,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1461,19 +1461,19 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="C30" s="12">
         <v>1500</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31" spans="1:5">
